--- a/xlsx/packagedata20260413 special cargo-FR-OT.xlsx
+++ b/xlsx/packagedata20260413 special cargo-FR-OT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Collection\ReactThreejsFiber\Containerloadingsys\public\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28B26E3-114E-4889-9707-A5679F739374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB7AEA2-E1D0-466B-BFC4-22062F030307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="19">
   <si>
     <t>否</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -39,10 +39,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>pkg05-54</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -88,6 +84,22 @@
   </si>
   <si>
     <t>Stackable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pkg02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pkg01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pkg03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pkg04</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -441,45 +453,45 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>10</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>11</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>12</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>13</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>14</v>
-      </c>
-      <c r="L1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B2">
         <v>350</v>
@@ -517,7 +529,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B3">
         <v>330</v>
@@ -555,7 +567,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="B4">
         <v>330</v>
@@ -593,7 +605,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B5">
         <v>330</v>
